--- a/multi seed generators/merged 10 seeds/classification/results/aggregated/privacy_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/classification/results/aggregated/privacy_mean_sd.xlsx
@@ -1682,12 +1682,10 @@
       <c r="O22" s="2" t="n">
         <v>0.9730864197530865</v>
       </c>
-      <c r="P22" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P22" s="2"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.973086 ± 0</t>
+          <t xml:space="preserve">0.973086</t>
         </is>
       </c>
       <c r="R22" s="2" t="n">
@@ -1753,12 +1751,10 @@
       <c r="O23" t="n">
         <v>5.509692938076826</v>
       </c>
-      <c r="P23" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P23"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.50969 ± 0</t>
+          <t xml:space="preserve">5.50969</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -1824,12 +1820,10 @@
       <c r="O24" s="2" t="n">
         <v>5.509692938076826</v>
       </c>
-      <c r="P24" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P24" s="2"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.50969 ± 0</t>
+          <t xml:space="preserve">5.50969</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
@@ -1895,12 +1889,10 @@
       <c r="O25" t="n">
         <v>5.475858305808769</v>
       </c>
-      <c r="P25" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P25"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.47586 ± 0</t>
+          <t xml:space="preserve">5.47586</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -1966,12 +1958,10 @@
       <c r="O26" s="2" t="n">
         <v>0.9066806772855166</v>
       </c>
-      <c r="P26" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P26" s="2"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.906681 ± 0</t>
+          <t xml:space="preserve">0.906681</t>
         </is>
       </c>
       <c r="R26" s="2" t="n">
@@ -2037,12 +2027,10 @@
       <c r="O27" t="n">
         <v>1.0</v>
       </c>
-      <c r="P27" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P27"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -2392,12 +2380,10 @@
       <c r="O32" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P32" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P32" s="2"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R32" s="2" t="n">
@@ -4522,12 +4508,10 @@
       <c r="O62" s="2" t="n">
         <v>0.9403245942571786</v>
       </c>
-      <c r="P62" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P62" s="2"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.940325 ± 0</t>
+          <t xml:space="preserve">0.940325</t>
         </is>
       </c>
       <c r="R62" s="2" t="n">
@@ -7362,12 +7346,10 @@
       <c r="O102" s="2" t="n">
         <v>0.6269135802469137</v>
       </c>
-      <c r="P102" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P102" s="2"/>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.626914 ± 0</t>
+          <t xml:space="preserve">0.626914</t>
         </is>
       </c>
       <c r="R102" s="2" t="n">
@@ -7433,12 +7415,10 @@
       <c r="O103" t="n">
         <v>4.569163692549475</v>
       </c>
-      <c r="P103" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P103"/>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.56916 ± 0</t>
+          <t xml:space="preserve">4.56916</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -7504,12 +7484,10 @@
       <c r="O104" s="2" t="n">
         <v>4.569163692549475</v>
       </c>
-      <c r="P104" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P104" s="2"/>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.56916 ± 0</t>
+          <t xml:space="preserve">4.56916</t>
         </is>
       </c>
       <c r="R104" s="2" t="n">
@@ -7575,12 +7553,10 @@
       <c r="O105" t="n">
         <v>4.160603666732447</v>
       </c>
-      <c r="P105" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P105"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1606 ± 0</t>
+          <t xml:space="preserve">4.1606</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -7646,12 +7622,10 @@
       <c r="O106" s="2" t="n">
         <v>0.8875044863435921</v>
       </c>
-      <c r="P106" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P106" s="2"/>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.887504 ± 0</t>
+          <t xml:space="preserve">0.887504</t>
         </is>
       </c>
       <c r="R106" s="2" t="n">
@@ -10202,12 +10176,10 @@
       <c r="O142" s="2" t="n">
         <v>0.8493827160493825</v>
       </c>
-      <c r="P142" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P142" s="2"/>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.849383 ± 0</t>
+          <t xml:space="preserve">0.849383</t>
         </is>
       </c>
       <c r="R142" s="2" t="n">
@@ -10273,12 +10245,10 @@
       <c r="O143" t="n">
         <v>5.872811690820016</v>
       </c>
-      <c r="P143" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P143"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.87281 ± 0</t>
+          <t xml:space="preserve">5.87281</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -10344,12 +10314,10 @@
       <c r="O144" s="2" t="n">
         <v>5.872811690820016</v>
       </c>
-      <c r="P144" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P144" s="2"/>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.87281 ± 0</t>
+          <t xml:space="preserve">5.87281</t>
         </is>
       </c>
       <c r="R144" s="2" t="n">
@@ -10415,12 +10383,10 @@
       <c r="O145" t="n">
         <v>5.995473117786184</v>
       </c>
-      <c r="P145" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P145"/>
       <c r="Q145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.99547 ± 0</t>
+          <t xml:space="preserve">5.99547</t>
         </is>
       </c>
       <c r="R145" t="n">
@@ -10486,12 +10452,10 @@
       <c r="O146" s="2" t="n">
         <v>0.894267111629128</v>
       </c>
-      <c r="P146" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P146" s="2"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.894267 ± 0</t>
+          <t xml:space="preserve">0.894267</t>
         </is>
       </c>
       <c r="R146" s="2" t="n">
@@ -13255,12 +13219,10 @@
       <c r="O185" t="n">
         <v>7.851049455002887</v>
       </c>
-      <c r="P185" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P185"/>
       <c r="Q185" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.85105 ± 0</t>
+          <t xml:space="preserve">7.85105</t>
         </is>
       </c>
       <c r="R185" t="n">
@@ -14462,12 +14424,10 @@
       <c r="O202" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P202" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P202" s="2"/>
       <c r="Q202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R202" s="2" t="n">
@@ -15882,12 +15842,10 @@
       <c r="O222" s="2" t="n">
         <v>0.5166666666666666</v>
       </c>
-      <c r="P222" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P222" s="2"/>
       <c r="Q222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.516667 ± 0</t>
+          <t xml:space="preserve">0.516667</t>
         </is>
       </c>
       <c r="R222" s="2" t="n">
@@ -15953,12 +15911,10 @@
       <c r="O223" t="n">
         <v>1004.076676288463</v>
       </c>
-      <c r="P223" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P223"/>
       <c r="Q223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004.08 ± 0</t>
+          <t xml:space="preserve">1004.08</t>
         </is>
       </c>
       <c r="R223" t="n">
@@ -16024,12 +15980,10 @@
       <c r="O224" s="2" t="n">
         <v>1004.076676288463</v>
       </c>
-      <c r="P224" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P224" s="2"/>
       <c r="Q224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004.08 ± 0</t>
+          <t xml:space="preserve">1004.08</t>
         </is>
       </c>
       <c r="R224" s="2" t="n">
@@ -16095,12 +16049,10 @@
       <c r="O225" t="n">
         <v>1041.435786799589</v>
       </c>
-      <c r="P225" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P225"/>
       <c r="Q225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041.44 ± 0</t>
+          <t xml:space="preserve">1041.44</t>
         </is>
       </c>
       <c r="R225" t="n">
@@ -16166,12 +16118,10 @@
       <c r="O226" s="2" t="n">
         <v>0.9377329116226886</v>
       </c>
-      <c r="P226" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P226" s="2"/>
       <c r="Q226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.937733 ± 0</t>
+          <t xml:space="preserve">0.937733</t>
         </is>
       </c>
       <c r="R226" s="2" t="n">
@@ -18722,12 +18672,10 @@
       <c r="O262" s="2" t="n">
         <v>0.5151851851851852</v>
       </c>
-      <c r="P262" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P262" s="2"/>
       <c r="Q262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.515185 ± 0</t>
+          <t xml:space="preserve">0.515185</t>
         </is>
       </c>
       <c r="R262" s="2" t="n">
@@ -18793,12 +18741,10 @@
       <c r="O263" t="n">
         <v>3.218485400316415</v>
       </c>
-      <c r="P263" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P263"/>
       <c r="Q263" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.21849 ± 0</t>
+          <t xml:space="preserve">3.21849</t>
         </is>
       </c>
       <c r="R263" t="n">
@@ -18864,12 +18810,10 @@
       <c r="O264" s="2" t="n">
         <v>3.218485400316415</v>
       </c>
-      <c r="P264" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P264" s="2"/>
       <c r="Q264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.21849 ± 0</t>
+          <t xml:space="preserve">3.21849</t>
         </is>
       </c>
       <c r="R264" s="2" t="n">
@@ -18935,12 +18879,10 @@
       <c r="O265" t="n">
         <v>3.1238356284859763</v>
       </c>
-      <c r="P265" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P265"/>
       <c r="Q265" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.12384 ± 0</t>
+          <t xml:space="preserve">3.12384</t>
         </is>
       </c>
       <c r="R265" t="n">
@@ -19006,12 +18948,10 @@
       <c r="O266" s="2" t="n">
         <v>0.9164697607326696</v>
       </c>
-      <c r="P266" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P266" s="2"/>
       <c r="Q266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.91647 ± 0</t>
+          <t xml:space="preserve">0.91647</t>
         </is>
       </c>
       <c r="R266" s="2" t="n">
@@ -21562,12 +21502,10 @@
       <c r="O302" s="2" t="n">
         <v>0.4569135802469136</v>
       </c>
-      <c r="P302" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P302" s="2"/>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.456914 ± 0</t>
+          <t xml:space="preserve">0.456914</t>
         </is>
       </c>
       <c r="R302" s="2" t="n">
@@ -21633,12 +21571,10 @@
       <c r="O303" t="n">
         <v>4.794378129434813</v>
       </c>
-      <c r="P303" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P303"/>
       <c r="Q303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.79438 ± 0</t>
+          <t xml:space="preserve">4.79438</t>
         </is>
       </c>
       <c r="R303" t="n">
@@ -21704,12 +21640,10 @@
       <c r="O304" s="2" t="n">
         <v>4.794378129434813</v>
       </c>
-      <c r="P304" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P304" s="2"/>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.79438 ± 0</t>
+          <t xml:space="preserve">4.79438</t>
         </is>
       </c>
       <c r="R304" s="2" t="n">
@@ -21775,12 +21709,10 @@
       <c r="O305" t="n">
         <v>4.490672237534019</v>
       </c>
-      <c r="P305" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P305"/>
       <c r="Q305" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.49067 ± 0</t>
+          <t xml:space="preserve">4.49067</t>
         </is>
       </c>
       <c r="R305" t="n">
@@ -21846,12 +21778,10 @@
       <c r="O306" s="2" t="n">
         <v>0.9231753038519461</v>
       </c>
-      <c r="P306" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P306" s="2"/>
       <c r="Q306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.923175 ± 0</t>
+          <t xml:space="preserve">0.923175</t>
         </is>
       </c>
       <c r="R306" s="2" t="n">
@@ -22272,12 +22202,10 @@
       <c r="O312" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P312" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P312" s="2"/>
       <c r="Q312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R312" s="2" t="n">
@@ -22627,12 +22555,10 @@
       <c r="O317" t="n">
         <v>1.0</v>
       </c>
-      <c r="P317" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P317"/>
       <c r="Q317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R317" t="n">
@@ -24402,12 +24328,10 @@
       <c r="O342" s="2" t="n">
         <v>0.6899999999999998</v>
       </c>
-      <c r="P342" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P342" s="2"/>
       <c r="Q342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.69 ± 0</t>
+          <t xml:space="preserve">0.69</t>
         </is>
       </c>
       <c r="R342" s="2" t="n">
@@ -24473,12 +24397,10 @@
       <c r="O343" t="n">
         <v>4.906632239160311</v>
       </c>
-      <c r="P343" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P343"/>
       <c r="Q343" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.90663 ± 0</t>
+          <t xml:space="preserve">4.90663</t>
         </is>
       </c>
       <c r="R343" t="n">
@@ -24544,12 +24466,10 @@
       <c r="O344" s="2" t="n">
         <v>4.906632239160311</v>
       </c>
-      <c r="P344" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P344" s="2"/>
       <c r="Q344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.90663 ± 0</t>
+          <t xml:space="preserve">4.90663</t>
         </is>
       </c>
       <c r="R344" s="2" t="n">
@@ -24615,12 +24535,10 @@
       <c r="O345" t="n">
         <v>4.706108650190693</v>
       </c>
-      <c r="P345" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P345"/>
       <c r="Q345" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.70611 ± 0</t>
+          <t xml:space="preserve">4.70611</t>
         </is>
       </c>
       <c r="R345" t="n">
@@ -24686,12 +24604,10 @@
       <c r="O346" s="2" t="n">
         <v>0.9254573824055351</v>
       </c>
-      <c r="P346" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P346" s="2"/>
       <c r="Q346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925457 ± 0</t>
+          <t xml:space="preserve">0.925457</t>
         </is>
       </c>
       <c r="R346" s="2" t="n">
